--- a/data/trans_camb/IP28_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,64</t>
+          <t>-1,38; 5,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,0</t>
+          <t>-3,8; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,87</t>
+          <t>-1,99; 2,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 3,5</t>
+          <t>-2,05; 3,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,0</t>
+          <t>-4,98; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,8</t>
+          <t>-3,39; 1,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,92</t>
+          <t>-1,22; 2,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; -0,32</t>
+          <t>-2,91; -0,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,76</t>
+          <t>-1,78; 1,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 3,37</t>
+          <t>-1,58; 2,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,21</t>
+          <t>-3,12; 1,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,9</t>
+          <t>-1,57; 3,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 3,11</t>
+          <t>-3,22; 3,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 0,0</t>
+          <t>-5,6; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 1,1</t>
+          <t>-4,73; 1,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,12</t>
+          <t>-1,97; 2,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,19</t>
+          <t>-2,76; 0,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,73</t>
+          <t>-2,34; 1,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 2,03</t>
+          <t>-5,1; 2,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 0,0</t>
+          <t>-6,93; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 0,31</t>
+          <t>-6,22; 0,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 4,71</t>
+          <t>-2,76; 4,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 7,13</t>
+          <t>-1,83; 6,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,02; -0,61</t>
+          <t>-5,54; -0,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,4</t>
+          <t>-2,6; 2,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,89</t>
+          <t>-2,34; 2,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,43</t>
+          <t>-4,37; -0,56</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-87,64; 348,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,74; 497,56</t>
+          <t>-84,38; 354,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,78</t>
+          <t>-0,48; 3,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,6</t>
+          <t>-0,99; 2,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,63</t>
+          <t>-1,56; 1,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,7</t>
+          <t>-1,43; 2,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,93</t>
+          <t>-2,55; 1,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,64</t>
+          <t>-2,98; 0,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,54</t>
+          <t>-0,33; 2,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,28</t>
+          <t>-1,13; 1,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,8</t>
+          <t>-1,54; 0,7</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-61,22; 1295,97</t>
+          <t>-62,17; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-77,25; inf</t>
+          <t>-80,82; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-65,58; 754,86</t>
+          <t>-66,77; 673,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-29,6; 405,98</t>
+          <t>-30,42; 379,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-73,28; 203,1</t>
+          <t>-70,58; 208,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-83,11; 159,79</t>
+          <t>-83,27; 158,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,0</t>
+          <t>-3,75; 3,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 1,12</t>
+          <t>-4,97; 1,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 4,68</t>
+          <t>-3,81; 4,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,7</t>
+          <t>-0,54; 3,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,12</t>
+          <t>-0,54; 3,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,11</t>
+          <t>-1,1; 2,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,88</t>
+          <t>-1,44; 2,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,6</t>
+          <t>-1,98; 1,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,31</t>
+          <t>-1,65; 2,25</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-85,04; 397,85</t>
+          <t>-86,8; 438,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,65; 505,64</t>
+          <t>-100,0; 451,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-58,28; 427,64</t>
+          <t>-62,71; 495,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-82,72; 289,99</t>
+          <t>-83,85; 246,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-70,24; 441,01</t>
+          <t>-76,27; 345,0</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 5,87</t>
+          <t>-2,92; 6,44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 2,42</t>
+          <t>-3,87; 2,35</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 5,22</t>
+          <t>-3,68; 5,09</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,68; 10,03</t>
+          <t>0,66; 8,52</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,95</t>
+          <t>-1,42; 2,84</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,03</t>
+          <t>-2,48; 1,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,22</t>
+          <t>-0,83; 4,81</t>
         </is>
       </c>
     </row>
@@ -1973,37 +1973,37 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,78</t>
+          <t>-0,59; 1,82</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,54</t>
+          <t>-1,44; 0,52</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,32</t>
+          <t>-1,11; 1,31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,67</t>
+          <t>-0,48; 1,61</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,53</t>
+          <t>-1,15; 0,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,67</t>
+          <t>-1,09; 0,84</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,34</t>
+          <t>-0,17; 1,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,69</t>
+          <t>-0,81; 0,61</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-32,24; 207,97</t>
+          <t>-34,18; 207,35</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-72,93; 72,08</t>
+          <t>-73,65; 73,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 151,92</t>
+          <t>-58,69; 134,96</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-32,5; 225,26</t>
+          <t>-33,04; 243,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-73,78; 71,7</t>
+          <t>-68,44; 98,3</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-66,96; 99,48</t>
+          <t>-67,27; 126,5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 139,49</t>
+          <t>-11,91; 149,33</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-63,01; 37,54</t>
+          <t>-63,97; 37,23</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 75,37</t>
+          <t>-51,52; 61,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP28_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 5,4</t>
+          <t>-1,37; 5,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,0</t>
+          <t>-3,58; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,8</t>
+          <t>-1,56; 2,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 3,41</t>
+          <t>-2,15; 3,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 0,0</t>
+          <t>-5,56; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,8</t>
+          <t>-3,58; 1,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,84</t>
+          <t>-1,25; 3,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; -0,32</t>
+          <t>-3,22; -0,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,48</t>
+          <t>-1,8; 1,58</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,85</t>
+          <t>-1,6; 2,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,23</t>
+          <t>-3,32; 1,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,9</t>
+          <t>-1,56; 3,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 3,04</t>
+          <t>-3,21; 2,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 0,0</t>
+          <t>-5,57; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 1,08</t>
+          <t>-4,13; 0,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 2,06</t>
+          <t>-1,6; 2,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 0,29</t>
+          <t>-2,86; 0,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,54</t>
+          <t>-1,99; 1,72</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 2,03</t>
+          <t>-5,04; 2,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 0,0</t>
+          <t>-6,77; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 0,32</t>
+          <t>-6,3; 0,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 4,84</t>
+          <t>-2,47; 4,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 6,9</t>
+          <t>-1,86; 7,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; -0,61</t>
+          <t>-5,54; -0,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,43</t>
+          <t>-2,78; 2,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 2,73</t>
+          <t>-2,38; 2,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; -0,56</t>
+          <t>-4,2; -0,37</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-80,54; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,64; 324,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,38; 354,62</t>
+          <t>-82,29; 407,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 3,88</t>
+          <t>-0,47; 3,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,51</t>
+          <t>-0,98; 2,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,71</t>
+          <t>-1,55; 1,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,93</t>
+          <t>-1,4; 2,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,07</t>
+          <t>-2,63; 0,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 0,61</t>
+          <t>-2,61; 0,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,46</t>
+          <t>-0,36; 2,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 1,24</t>
+          <t>-1,16; 1,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,7</t>
+          <t>-1,42; 0,85</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-62,17; —</t>
+          <t>-66,83; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-80,82; —</t>
+          <t>-72,78; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-66,77; 673,25</t>
+          <t>-69,19; 583,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,42; 379,65</t>
+          <t>-26,79; 425,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-70,58; 208,58</t>
+          <t>-68,47; 222,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-83,27; 158,36</t>
+          <t>-84,2; 216,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 3,17</t>
+          <t>-3,79; 3,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 1,25</t>
+          <t>-5,0; 1,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 4,51</t>
+          <t>-3,61; 4,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,89</t>
+          <t>-0,57; 4,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,52</t>
+          <t>-1,03; 3,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,12</t>
+          <t>-1,12; 2,11</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,56</t>
+          <t>-1,29; 2,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,47</t>
+          <t>-2,09; 1,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,25</t>
+          <t>-1,61; 2,48</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-86,8; 438,66</t>
+          <t>-89,06; 505,18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 451,03</t>
+          <t>-100,0; 620,6</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-62,71; 495,04</t>
+          <t>-60,32; 571,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-83,85; 246,52</t>
+          <t>-83,59; 324,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-76,27; 345,0</t>
+          <t>-77,43; 387,72</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 6,44</t>
+          <t>-2,91; 5,98</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 2,35</t>
+          <t>-4,26; 2,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 5,09</t>
+          <t>-3,69; 5,31</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,66; 8,52</t>
+          <t>0,7; 9,98</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,84</t>
+          <t>-1,66; 2,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,03</t>
+          <t>-2,39; 1,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 4,81</t>
+          <t>-0,7; 5,13</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,82</t>
+          <t>-0,59; 1,79</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,52</t>
+          <t>-1,4; 0,57</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,31</t>
+          <t>-1,1; 1,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,61</t>
+          <t>-0,56; 1,66</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,63</t>
+          <t>-1,25; 0,59</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,84</t>
+          <t>-1,11; 0,77</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,41</t>
+          <t>-0,23; 1,35</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,33</t>
+          <t>-0,99; 0,38</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,61</t>
+          <t>-0,81; 0,7</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-34,18; 207,35</t>
+          <t>-32,48; 221,44</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-73,65; 73,44</t>
+          <t>-72,87; 61,05</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-58,69; 134,96</t>
+          <t>-60,25; 153,9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-33,04; 243,91</t>
+          <t>-36,93; 221,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-68,44; 98,3</t>
+          <t>-73,91; 95,18</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-67,27; 126,5</t>
+          <t>-65,94; 113,02</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 149,33</t>
+          <t>-15,25; 143,64</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-63,97; 37,23</t>
+          <t>-60,27; 49,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-51,52; 61,95</t>
+          <t>-48,93; 77,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP28_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP28_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,05</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,77</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,39</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 5,27</t>
+          <t>-2,09; 3,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 0,0</t>
+          <t>-4,73; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,75</t>
+          <t>-3,01; 1,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,43</t>
+          <t>-1,4; 4,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 0,0</t>
+          <t>-3,82; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 1,7</t>
+          <t>-1,55; 3,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,02</t>
+          <t>-1,07; 2,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,22; -0,32</t>
+          <t>-3,16; -0,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,58</t>
+          <t>-1,67; 1,94</t>
         </is>
       </c>
     </row>
@@ -730,47 +730,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-14,61%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>136,79%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>17,26%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>30,78%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>59,6%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-17,82%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>59,6%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-3,18%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,58</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,03</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,14</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,18</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,58</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,83</t>
+          <t>-2,43; 3,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 1,2</t>
+          <t>-4,75; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,88</t>
+          <t>-4,46; 0,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,57</t>
+          <t>-1,58; 3,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 0,0</t>
+          <t>-3,12; 1,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 0,65</t>
+          <t>-1,54; 4,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,0</t>
+          <t>-1,95; 2,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,19</t>
+          <t>-2,78; 0,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,72</t>
+          <t>-1,85; 1,73</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-0,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-65,32%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>17,95%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-22,87%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>102,37%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-60,07%</t>
+          <t>105,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-6,41%</t>
+          <t>-7,34%</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-2,04</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,97</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,99</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,67</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,04</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-1,57</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 2,02</t>
+          <t>-2,51; 4,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,0</t>
+          <t>-1,72; 7,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 0,32</t>
+          <t>-6,02; -0,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,9</t>
+          <t>-5,04; 2,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 7,14</t>
+          <t>-6,83; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,54; -0,6</t>
+          <t>-5,21; 1,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 2,46</t>
+          <t>-2,7; 2,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 2,89</t>
+          <t>-2,72; 2,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,2; -0,37</t>
+          <t>-3,74; 0,12</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>88,11%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-48,87%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-83,9%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>88,11%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-52,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-92,95%</t>
+          <t>-77,73%</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-80,54; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-85,64; 324,4</t>
+          <t>-87,64; 348,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,29; 407,43</t>
+          <t>-85,74; 497,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1272,47 +1272,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,67</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,78</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,66</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0,01</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,68</t>
+          <t>-1,35; 2,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,63</t>
+          <t>-2,45; 0,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,67</t>
+          <t>-2,69; 0,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 2,67</t>
+          <t>-0,49; 3,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,8</t>
+          <t>-0,94; 2,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,77</t>
+          <t>-1,41; 2,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,45</t>
+          <t>-0,35; 2,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,27</t>
+          <t>-1,29; 1,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,85</t>
+          <t>-1,42; 0,96</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>50,94%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-47,99%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-55,83%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>135,04%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>69,59%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>50,94%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-47,99%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-53,81%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-31,36%</t>
+          <t>-24,41%</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1431,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,83; —</t>
+          <t>-65,58; 754,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-72,78; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-69,19; 583,03</t>
+          <t>-61,22; 1295,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,25; inf</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 425,84</t>
+          <t>-29,6; 405,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-68,47; 222,14</t>
+          <t>-73,28; 203,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-84,2; 216,62</t>
+          <t>-80,25; 192,77</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,53</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-0,12</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,48</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,39</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,53</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 3,05</t>
+          <t>-0,57; 3,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,45</t>
+          <t>-0,54; 3,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 4,48</t>
+          <t>-1,07; 2,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 4,26</t>
+          <t>-4,12; 3,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,05</t>
+          <t>-5,41; 1,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,11</t>
+          <t>-3,15; 4,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,75</t>
+          <t>-1,23; 2,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,4</t>
+          <t>-2,08; 1,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,48</t>
+          <t>-1,33; 2,67</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>235,4%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>195,84%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>102,99%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-4,33%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-55,58%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>235,4%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>195,84%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-89,06; 505,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 620,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,04; 397,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,37; 544,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-60,32; 571,15</t>
+          <t>-58,28; 427,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-83,59; 324,43</t>
+          <t>-82,72; 289,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-77,43; 387,72</t>
+          <t>-68,12; 463,78</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3,38</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,9</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-0,82</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>-0,15</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,58</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 5,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 2,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,31</t>
+          <t>0,64; 10,54</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,88; 5,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,96; 2,42</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,7; 9,98</t>
+          <t>-3,67; 5,35</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,57</t>
+          <t>-1,51; 2,95</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,03</t>
+          <t>-2,18; 1,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 5,13</t>
+          <t>-0,62; 5,35</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>47,26%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-43,16%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-8,49%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>-7,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>158,76%</t>
+          <t>162,01%</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,53</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-0,17</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,56</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-0,44</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 1,79</t>
+          <t>-0,45; 1,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,57</t>
+          <t>-1,25; 0,53</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,19</t>
+          <t>-1,07; 0,74</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,66</t>
+          <t>-0,58; 1,78</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,59</t>
+          <t>-1,46; 0,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,77</t>
+          <t>-0,97; 1,62</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,35</t>
+          <t>-0,26; 1,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,38</t>
+          <t>-1,07; 0,33</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,7</t>
+          <t>-0,7; 0,84</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>44,53%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-22,17%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-14,55%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>39,97%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-31,27%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>44,53%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-22,17%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-16,73%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-6,53%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 221,44</t>
+          <t>-32,5; 225,26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-72,87; 61,05</t>
+          <t>-73,78; 71,7</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-60,25; 153,9</t>
+          <t>-66,2; 102,96</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 221,19</t>
+          <t>-32,24; 207,97</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-73,91; 95,18</t>
+          <t>-72,93; 72,08</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-65,94; 113,02</t>
+          <t>-50,34; 198,46</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 143,64</t>
+          <t>-16,23; 139,49</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-60,27; 49,56</t>
+          <t>-63,01; 37,54</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-48,93; 77,63</t>
+          <t>-43,64; 91,04</t>
         </is>
       </c>
     </row>
